--- a/docs/dossiers/dossier-vente-murs-libres-98-m2-l-ile-saint-denis-3e6f4aca.xlsx
+++ b/docs/dossiers/dossier-vente-murs-libres-98-m2-l-ile-saint-denis-3e6f4aca.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-vente-murs-libres-98-m2-l-ile-saint-denis-3e6f4aca.xlsx
+++ b/docs/dossiers/dossier-vente-murs-libres-98-m2-l-ile-saint-denis-3e6f4aca.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-vente-murs-libres-98-m2-l-ile-saint-denis-3e6f4aca.xlsx
+++ b/docs/dossiers/dossier-vente-murs-libres-98-m2-l-ile-saint-denis-3e6f4aca.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-vente-murs-libres-98-m2-l-ile-saint-denis-3e6f4aca.xlsx
+++ b/docs/dossiers/dossier-vente-murs-libres-98-m2-l-ile-saint-denis-3e6f4aca.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-vente-murs-libres-98-m2-l-ile-saint-denis-3e6f4aca.xlsx
+++ b/docs/dossiers/dossier-vente-murs-libres-98-m2-l-ile-saint-denis-3e6f4aca.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>65/100</t>
+          <t>63/100</t>
         </is>
       </c>
       <c r="C57" s="19" t="inlineStr">

--- a/docs/dossiers/dossier-vente-murs-libres-98-m2-l-ile-saint-denis-3e6f4aca.xlsx
+++ b/docs/dossiers/dossier-vente-murs-libres-98-m2-l-ile-saint-denis-3e6f4aca.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-vente-murs-libres-98-m2-l-ile-saint-denis-3e6f4aca.xlsx
+++ b/docs/dossiers/dossier-vente-murs-libres-98-m2-l-ile-saint-denis-3e6f4aca.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-vente-murs-libres-98-m2-l-ile-saint-denis-3e6f4aca.xlsx
+++ b/docs/dossiers/dossier-vente-murs-libres-98-m2-l-ile-saint-denis-3e6f4aca.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-vente-murs-libres-98-m2-l-ile-saint-denis-3e6f4aca.xlsx
+++ b/docs/dossiers/dossier-vente-murs-libres-98-m2-l-ile-saint-denis-3e6f4aca.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
